--- a/public/templates/Brokers Import File.xlsx
+++ b/public/templates/Brokers Import File.xlsx
@@ -1,42 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pngor\OneDrive\Desktop\Gonyeti\excel files\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13561E8A-993F-4C75-A26F-B5802E9267AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1BF86B54-598F-4454-AEBC-072642D0AD6D}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
   <si>
     <t>name</t>
   </si>
@@ -60,41 +39,86 @@
   </si>
   <si>
     <t>streetaddress</t>
+  </si>
+  <si>
+    <t>ops@swiftbrokers.co.zw</t>
+  </si>
+  <si>
+    <t>+263 77 345 6789</t>
+  </si>
+  <si>
+    <t>+263 242 700100</t>
+  </si>
+  <si>
+    <t>#Swift Freight Brokers</t>
+  </si>
+  <si>
+    <t>Zimbabwe</t>
+  </si>
+  <si>
+    <t>Harare</t>
+  </si>
+  <si>
+    <t>Southerton</t>
+  </si>
+  <si>
+    <t>45 Seke Rd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b val="0"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -107,12 +131,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -121,63 +145,45 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+  <cellXfs count="10">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" quotePrefix="1" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="4" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="3" quotePrefix="1" numFmtId="49" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -224,7 +230,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -276,7 +282,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -337,154 +343,190 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{962EA1E7-8F34-4D1F-81EC-AB63C2A66708}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:Q32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="10" width="25.109375" customWidth="1"/>
+    <col min="1" max="1" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="13.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="25.109375" customWidth="true" style="0"/>
+    <col min="10" max="10" width="25.109375" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" customHeight="1" ht="20.25" s="4" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,149 +561,344 @@
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17">
+      <c r="A2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6"/>
       <c r="B6" s="5"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7"/>
       <c r="B7" s="5"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16"/>
+      <c r="B16"/>
       <c r="C16" s="6"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19"/>
       <c r="B19" s="5"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20"/>
+      <c r="B20"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21"/>
       <c r="B21" s="5"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22"/>
       <c r="B22" s="5"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23"/>
+      <c r="B23"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24"/>
+      <c r="B24"/>
       <c r="C24" s="6"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25"/>
       <c r="B25" s="5"/>
       <c r="C25" s="6"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26"/>
       <c r="B26" s="5"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27"/>
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28"/>
       <c r="B28" s="5"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29"/>
       <c r="B29" s="5"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30"/>
+      <c r="B30"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31"/>
       <c r="B31" s="5"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32"/>
       <c r="B32" s="5"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>